--- a/api/templates/module_activity_report/en.xlsx
+++ b/api/templates/module_activity_report/en.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\ahernandez\repos\aspect\api\templates\module_activity_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6B00C9-DBAE-430A-A378-988E321ADE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE50B2A-F1A6-4B8E-B2D1-BE4149B70713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3EE22C30-721D-4358-A9D5-5FEF2B321F4D}"/>
   </bookViews>
   <sheets>
     <sheet name="ModuleActivity" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ModuleActivity!$A$7:$G$8</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,28 +38,73 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Header 1</t>
-  </si>
-  <si>
-    <t>Header 3</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
-    <t>&lt;message&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Lgas&gt;</t>
+    <t>&lt;deviceName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;moduleName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;moduleSerial&gt;</t>
+  </si>
+  <si>
+    <t>&lt;lastSeen&gt;</t>
+  </si>
+  <si>
+    <t>Device Name</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Module Serial</t>
+  </si>
+  <si>
+    <t>Last Seen</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>&lt;#&gt;</t>
+  </si>
+  <si>
+    <t>Date Range:  &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Last Issue</t>
+  </si>
+  <si>
+    <t>&lt;lastIssue&gt;</t>
+  </si>
+  <si>
+    <t>Module Activity Report</t>
+  </si>
+  <si>
+    <t>Cities: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>Provinces:  &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Date Last Issue</t>
+  </si>
+  <si>
+    <t>&lt;dateLastIssue&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,16 +112,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CC0DD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -81,12 +154,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,38 +515,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6D6E8E-8E83-4696-9E0F-45AB9A05EF97}">
-  <dimension ref="A2:B8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="42" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
+    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="3"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="C8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A7:G8" xr:uid="{5D6D6E8E-8E83-4696-9E0F-45AB9A05EF97}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/api/templates/module_activity_report/en.xlsx
+++ b/api/templates/module_activity_report/en.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\ahernandez\repos\aspect\api\templates\module_activity_report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\module_activity_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE50B2A-F1A6-4B8E-B2D1-BE4149B70713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C105662-97A6-4017-8797-D80D4182DC06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3EE22C30-721D-4358-A9D5-5FEF2B321F4D}"/>
   </bookViews>
@@ -85,16 +85,16 @@
     <t>Module Activity Report</t>
   </si>
   <si>
-    <t>Cities: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>Provinces:  &lt;States&gt;</t>
-  </si>
-  <si>
     <t>Date Last Issue</t>
   </si>
   <si>
     <t>&lt;dateLastIssue&gt;</t>
+  </si>
+  <si>
+    <t>States/Provinces:  &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Cities/Lgas: &lt;Lgas&gt;</t>
   </si>
 </sst>
 </file>
@@ -541,13 +541,13 @@
     </row>
     <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4" s="4"/>
     </row>
@@ -573,7 +573,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>12</v>
@@ -596,7 +596,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>

--- a/api/templates/module_activity_report/en.xlsx
+++ b/api/templates/module_activity_report/en.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\module_activity_report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\module_activity_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C105662-97A6-4017-8797-D80D4182DC06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3EE22C30-721D-4358-A9D5-5FEF2B321F4D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="ModuleActivity" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ModuleActivity!$A$7:$G$8</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -91,16 +90,16 @@
     <t>&lt;dateLastIssue&gt;</t>
   </si>
   <si>
-    <t>States/Provinces:  &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>Cities/Lgas: &lt;Lgas&gt;</t>
+    <t>&lt;StatesLabel&gt;:  &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
@@ -205,8 +204,36 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD7D7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -514,7 +541,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6D6E8E-8E83-4696-9E0F-45AB9A05EF97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -603,7 +630,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:G8" xr:uid="{5D6D6E8E-8E83-4696-9E0F-45AB9A05EF97}"/>
+  <autoFilter ref="A7:G8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/api/templates/module_activity_report/en.xlsx
+++ b/api/templates/module_activity_report/en.xlsx
@@ -1,29 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/module_activity_report/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099897EB-A4B8-EB4B-9FB9-6D3D7EC6D028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580"/>
   </bookViews>
   <sheets>
-    <sheet name="Module Activity" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Module Activity" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Module Activity'!$A$8:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase">'Module Activity'!$A$8:$G$9</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Module Activity Report</t>
   </si>
@@ -46,6 +40,9 @@
     <t>Device Name</t>
   </si>
   <si>
+    <t>Site</t>
+  </si>
+  <si>
     <t>Module Name</t>
   </si>
   <si>
@@ -65,6 +62,9 @@
   </si>
   <si>
     <t>&lt;deviceName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>&lt;moduleName&gt;</t>
@@ -85,34 +85,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -374,52 +376,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.6640625"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.5" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="42" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
@@ -441,33 +444,41 @@
       <c r="G8" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="H8" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="C9" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="7" t="s">
         <v>16</v>
       </c>
+      <c r="E9" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="F9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
+      <c r="G9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A8:G9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <autoFilter ref="A8:G9"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/module_activity_report/en.xlsx
+++ b/api/templates/module_activity_report/en.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD2133D-42A7-A145-A074-A6B5FF94A18C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Module Activity" state="visible" r:id="rId4"/>
+    <sheet name="Module Activity" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Module Activity'!$A$8:$G$9</definedName>
@@ -85,36 +86,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
       <color indexed="64"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color indexed="64"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -376,13 +377,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.6640625"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="36.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="18.5" customWidth="1"/>
     <col min="6" max="6" width="16.5" customWidth="1"/>
@@ -390,39 +391,39 @@
     <col min="8" max="8" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2"/>
     </row>
-    <row r="3" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
@@ -448,7 +449,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
@@ -474,11 +475,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A8:G9"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <autoFilter ref="A8:G9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/module_activity_report/en.xlsx
+++ b/api/templates/module_activity_report/en.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD2133D-42A7-A145-A074-A6B5FF94A18C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580"/>
   </bookViews>
   <sheets>
-    <sheet name="Module Activity" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Module Activity" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Module Activity'!$A$8:$G$9</definedName>
@@ -18,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Module Activity Report</t>
   </si>
@@ -30,6 +29,9 @@
   </si>
   <si>
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+  </si>
+  <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -86,36 +88,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <color indexed="64"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -377,9 +379,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.6640625"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -391,93 +393,98 @@
     <col min="8" max="8" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:G9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <autoFilter ref="A8:G9"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/module_activity_report/en.xlsx
+++ b/api/templates/module_activity_report/en.xlsx
@@ -176,10 +176,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -421,7 +422,7 @@
       <c r="B5" s="2"/>
     </row>
     <row r="6" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -431,54 +432,54 @@
       </c>
     </row>
     <row r="8" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="7" t="s">
         <v>21</v>
       </c>
     </row>

--- a/api/templates/module_activity_report/en.xlsx
+++ b/api/templates/module_activity_report/en.xlsx
@@ -31,7 +31,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Decommissioned Devices: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -176,11 +176,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -422,7 +421,7 @@
       <c r="B5" s="2"/>
     </row>
     <row r="6" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -432,54 +431,54 @@
       </c>
     </row>
     <row r="8" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>21</v>
       </c>
     </row>
